--- a/Logs/Accounts.XLSX
+++ b/Logs/Accounts.XLSX
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18150" windowHeight="10215"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13740" windowHeight="10215"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="37">
   <si>
     <t>Email</t>
   </si>
@@ -77,6 +77,9 @@
     <t>Frank</t>
   </si>
   <si>
+    <t>4321</t>
+  </si>
+  <si>
     <t>emmastock@gmail.com</t>
   </si>
   <si>
@@ -104,6 +107,9 @@
     <t>John Doe</t>
   </si>
   <si>
+    <t>1234</t>
+  </si>
+  <si>
     <t>Lv4</t>
   </si>
   <si>
@@ -113,6 +119,9 @@
     <t>Mike</t>
   </si>
   <si>
+    <t>1111</t>
+  </si>
+  <si>
     <t>Lv2</t>
   </si>
   <si>
@@ -123,6 +132,9 @@
   </si>
   <si>
     <t>admin</t>
+  </si>
+  <si>
+    <t>2409</t>
   </si>
 </sst>
 </file>
@@ -138,15 +150,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -154,12 +172,34 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -442,185 +482,193 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.28515625" style="2" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="3">
         <v>23425946</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="3">
         <v>2</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C4">
-        <v>4321</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="C4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="3">
         <v>0</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="A5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C5" t="s">
+      <c r="B5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D5" t="s">
+      <c r="C5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E5">
+      <c r="D5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="3">
         <v>94222958</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="A6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C6" t="s">
+      <c r="B6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D6" t="s">
+      <c r="C6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="3">
         <v>957410</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="A7" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C7">
-        <v>1234</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="B7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E7">
+      <c r="C7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="3">
         <v>6</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8">
-        <v>1111</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="A8" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E8">
+      <c r="B8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="3">
         <v>349634628</v>
       </c>
-      <c r="F8" t="s">
-        <v>30</v>
+      <c r="F8" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9">
-        <v>2409</v>
-      </c>
-      <c r="D9" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9">
+      <c r="A9" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="3">
         <v>943361841</v>
       </c>
-      <c r="F9" t="s">
-        <v>30</v>
+      <c r="F9" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
